--- a/camp_registration_forms/046_girl_scout_product_permission_form--camp_registration_forms.xlsx
+++ b/camp_registration_forms/046_girl_scout_product_permission_form--camp_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_$50',_'value':_1}</t>
+          <t>less_than_$50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Less than $50', 'value': 1}</t>
+          <t>Less than $50</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'$50-$100',_'value':_2}</t>
+          <t>$50-$100</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '$50-$100', 'value': 2}</t>
+          <t>$50-$100</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'over_$100',_'value':_3}</t>
+          <t>over_$100</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Over $100', 'value': 3}</t>
+          <t>Over $100</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cookie',_'value':_1}</t>
+          <t>cookie</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Cookie', 'value': 1}</t>
+          <t>Cookie</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'candy',_'value':_2}</t>
+          <t>candy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Candy', 'value': 2}</t>
+          <t>Candy</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'beverage',_'value':_3}</t>
+          <t>beverage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Beverage', 'value': 3}</t>
+          <t>Beverage</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'14_day',_'value':_1}</t>
+          <t>14_day</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '14 day', 'value': 1}</t>
+          <t>14 day</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'28_day',_'value':_2}</t>
+          <t>28_day</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '28 day', 'value': 2}</t>
+          <t>28 day</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'30_day',_'value':_3}</t>
+          <t>30_day</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '30 day', 'value': 3}</t>
+          <t>30 day</t>
         </is>
       </c>
     </row>
